--- a/data/trans_camb/P16A13-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,47</t>
+          <t>0,18; 4,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,03</t>
+          <t>-1,85; 2,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 11,04</t>
+          <t>5,65; 11,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,53</t>
+          <t>0,65; 4,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,07</t>
+          <t>-0,42; 3,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 15,37</t>
+          <t>10,32; 15,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,96</t>
+          <t>1,28; 4,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,42</t>
+          <t>-0,37; 2,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 12,64</t>
+          <t>9,4; 13,0</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 121,56</t>
+          <t>0,13; 120,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 54,2</t>
+          <t>-34,22; 53,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105,73; 297,74</t>
+          <t>103,8; 297,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 99,03</t>
+          <t>8,43; 95,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 85,92</t>
+          <t>-6,67; 79,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>158,26; 327,41</t>
+          <t>158,47; 332,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,27; 87,37</t>
+          <t>21,55; 90,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 53,54</t>
+          <t>-7,4; 56,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>157,9; 281,18</t>
+          <t>161,74; 283,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,47</t>
+          <t>0,45; 2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,83</t>
+          <t>0,06; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,48</t>
+          <t>1,56; 4,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,86</t>
+          <t>-0,66; 1,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,11</t>
+          <t>-1,12; 1,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,81</t>
+          <t>1,01; 3,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,8</t>
+          <t>0,26; 1,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,28</t>
+          <t>-0,22; 1,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,78</t>
+          <t>1,87; 3,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,71; 226,8</t>
+          <t>20,61; 245,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 180,35</t>
+          <t>-0,22; 191,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,3; 423,87</t>
+          <t>91,86; 441,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 84,2</t>
+          <t>-21,13; 90,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 52,44</t>
+          <t>-34,52; 52,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,87; 175,06</t>
+          <t>32,68; 176,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 104,55</t>
+          <t>10,02; 110,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 74,93</t>
+          <t>-9,92; 71,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,51; 219,92</t>
+          <t>83,13; 228,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,59</t>
+          <t>-1,38; 3,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,02</t>
+          <t>-1,99; 2,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,77</t>
+          <t>0,71; 5,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,48</t>
+          <t>1,57; 6,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,0</t>
+          <t>0,01; 3,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,97</t>
+          <t>1,47; 4,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,09</t>
+          <t>0,59; 4,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,33</t>
+          <t>-0,71; 2,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,21</t>
+          <t>1,61; 4,41</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 196,78</t>
+          <t>-41,95; 190,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 108,72</t>
+          <t>-57,32; 122,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 269,99</t>
+          <t>13,69; 276,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,04; 802,57</t>
+          <t>54,27; 896,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 580,08</t>
+          <t>-9,27; 441,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,43; 712,0</t>
+          <t>54,9; 730,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,95; 259,84</t>
+          <t>18,32; 259,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 146,72</t>
+          <t>-27,48; 144,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48,61; 262,38</t>
+          <t>46,7; 286,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,45</t>
+          <t>0,57; 2,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,13</t>
+          <t>-0,52; 1,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,53</t>
+          <t>1,81; 4,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,74</t>
+          <t>0,75; 2,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,36</t>
+          <t>-0,48; 1,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,23</t>
+          <t>2,63; 5,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,27</t>
+          <t>1,01; 2,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,06</t>
+          <t>-0,22; 1,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,65</t>
+          <t>2,81; 4,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,29; 107,58</t>
+          <t>18,29; 110,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 50,89</t>
+          <t>-18,01; 49,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66,71; 192,9</t>
+          <t>62,02; 200,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,66; 86,29</t>
+          <t>19,1; 90,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 43,11</t>
+          <t>-11,65; 46,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,75; 165,24</t>
+          <t>74,66; 169,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,11; 79,2</t>
+          <t>29,34; 85,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 36,46</t>
+          <t>-6,48; 37,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>83,8; 166,42</t>
+          <t>81,74; 159,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A13-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,89</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,08</t>
+          <t>10,51</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,68</t>
+          <t>0,17; 4,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,04</t>
+          <t>-1,82; 2,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,36</t>
+          <t>5,07; 10,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,46</t>
+          <t>0,91; 4,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,96</t>
+          <t>-0,44; 4,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 15,15</t>
+          <t>10,31; 14,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,08</t>
+          <t>1,27; 4,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,6</t>
+          <t>-0,41; 2,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,0</t>
+          <t>8,76; 12,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183,24%</t>
+          <t>167,42%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>233,87%</t>
+          <t>226,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>217,56%</t>
+          <t>206,34%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 120,84</t>
+          <t>3,19; 120,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 53,31</t>
+          <t>-34,3; 62,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103,8; 297,84</t>
+          <t>96,72; 290,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 95,27</t>
+          <t>14,03; 99,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 79,97</t>
+          <t>-7,58; 84,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>158,47; 332,61</t>
+          <t>158,56; 324,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,55; 90,54</t>
+          <t>22,14; 92,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 56,44</t>
+          <t>-7,32; 52,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>161,74; 283,19</t>
+          <t>148,58; 270,2</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>3,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,45</t>
+          <t>0,42; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,97</t>
+          <t>0,02; 1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,33</t>
+          <t>2,42; 4,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,87</t>
+          <t>-0,71; 1,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,1</t>
+          <t>-1,02; 1,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,77</t>
+          <t>2,03; 4,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,85</t>
+          <t>0,2; 1,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,19</t>
+          <t>-0,28; 1,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,83</t>
+          <t>2,63; 4,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>223,98%</t>
+          <t>241,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>123,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>143,14%</t>
+          <t>166,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,61; 245,25</t>
+          <t>17,16; 237,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 191,33</t>
+          <t>-0,64; 174,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,86; 441,4</t>
+          <t>119,24; 458,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 90,52</t>
+          <t>-21,09; 82,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 52,61</t>
+          <t>-31,49; 51,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,68; 176,12</t>
+          <t>60,15; 210,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 110,86</t>
+          <t>7,18; 110,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 71,17</t>
+          <t>-12,1; 68,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,13; 228,27</t>
+          <t>107,98; 266,22</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,59</t>
+          <t>-1,56; 3,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,14</t>
+          <t>-2,29; 2,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,01</t>
+          <t>0,96; 5,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,54</t>
+          <t>1,74; 6,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,71</t>
+          <t>-0,08; 4,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,86</t>
+          <t>1,73; 4,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,08</t>
+          <t>0,64; 4,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,35</t>
+          <t>-0,58; 2,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,41</t>
+          <t>1,93; 4,64</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>107,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>221,94%</t>
+          <t>237,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>134,5%</t>
+          <t>144,6%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,95; 190,46</t>
+          <t>-40,65; 205,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 122,44</t>
+          <t>-59,37; 119,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,69; 276,62</t>
+          <t>20,99; 314,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54,27; 896,29</t>
+          <t>55,97; 889,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 441,51</t>
+          <t>-19,59; 573,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,9; 730,66</t>
+          <t>63,95; 762,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 259,68</t>
+          <t>16,22; 246,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 144,13</t>
+          <t>-22,47; 145,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46,7; 286,65</t>
+          <t>59,63; 302,72</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>4,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,44</t>
+          <t>0,48; 2,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,09</t>
+          <t>-0,54; 1,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,57</t>
+          <t>2,66; 4,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,86</t>
+          <t>0,78; 2,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,44</t>
+          <t>-0,46; 1,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,28</t>
+          <t>3,84; 5,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,39</t>
+          <t>0,95; 2,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,05</t>
+          <t>-0,24; 0,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,62</t>
+          <t>3,53; 4,84</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127,44%</t>
+          <t>136,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>117,94%</t>
+          <t>133,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>122,25%</t>
+          <t>134,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,29; 110,33</t>
+          <t>14,17; 102,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 49,8</t>
+          <t>-18,4; 46,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62,02; 200,13</t>
+          <t>86,06; 199,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,1; 90,61</t>
+          <t>18,77; 83,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 46,99</t>
+          <t>-11,39; 44,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,66; 169,9</t>
+          <t>94,56; 183,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,34; 85,9</t>
+          <t>27,82; 81,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 37,34</t>
+          <t>-7,13; 33,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>81,74; 159,66</t>
+          <t>101,9; 171,45</t>
         </is>
       </c>
     </row>
